--- a/questions.xlsx
+++ b/questions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Clod\Desktop\Game Ideas\Gramaticescu\gramaticescu-doua-repository-uri\gramaticescu-intrebari\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D023914-ADBF-491D-9785-3E22C189B149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEF3FC8C-988D-4E34-8DBD-A8EA4B379FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17100" yWindow="765" windowWidth="38700" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11385" yWindow="885" windowWidth="38700" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Întrebări" sheetId="1" r:id="rId1"/>
@@ -2104,7 +2104,7 @@
     <t>După ce urci fișierul pe GitHub, verificarea și publicarea se fac automat. Dacă există o greșeală, publicarea se oprește și vezi rândul greșit în tabul „Actions”.</t>
   </si>
   <si>
-    <t>Mariana ___ jucat în parc.</t>
+    <t>Maria ___ jucat în parc.</t>
   </si>
 </sst>
 </file>
